--- a/output/descriptif_territorial.xlsx
+++ b/output/descriptif_territorial.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="occitanie_part_region" sheetId="1" r:id="rId1"/>
-    <sheet name="occitanie_part_nationalite" sheetId="2" r:id="rId2"/>
-    <sheet name="regions" sheetId="3" r:id="rId3"/>
+    <sheet name="top_pays_idf_2024_region" sheetId="2" r:id="rId2"/>
+    <sheet name="occitanie_part_nationalite" sheetId="3" r:id="rId3"/>
+    <sheet name="regions" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -536,28 +537,28 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>part_occitanie</t>
+          <t>part_idf</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAROC</t>
+          <t>ALGERIE</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.09366939553661545</v>
+        <v>0.1007988368400822</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALGERIE</t>
+          <t>MAROC</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.07902439024390244</v>
+        <v>0.08501428881795545</v>
       </c>
     </row>
     <row r="4">
@@ -567,17 +568,17 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.07254555636927584</v>
+        <v>0.07812056085699484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SENEGAL</t>
+          <t>ITALIE</t>
         </is>
       </c>
       <c r="B5">
-        <v>0.09554535302146669</v>
+        <v>0.0589518191085783</v>
       </c>
     </row>
     <row r="6">
@@ -587,47 +588,47 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.1058588036030487</v>
+        <v>0.04712803115129435</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESPAGNE</t>
+          <t>SENEGAL</t>
         </is>
       </c>
       <c r="B7">
-        <v>0.1464467396331124</v>
+        <v>0.03591423366813176</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LIBAN</t>
+          <t>CAMEROUN</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.09932375316990702</v>
+        <v>0.03332386316158898</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ITALIE</t>
+          <t>INDE</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.06785101142046727</v>
+        <v>0.03278907699249628</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BENIN</t>
+          <t>LIBAN</t>
         </is>
       </c>
       <c r="B10">
-        <v>0.1038307751837998</v>
+        <v>0.03149389173922489</v>
       </c>
     </row>
     <row r="11">
@@ -637,57 +638,57 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.07771507771507771</v>
+        <v>0.02942995136788275</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GABON</t>
+          <t>ETATS-UNIS</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.1343088010482638</v>
+        <v>0.02837709109748149</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MADAGASCAR</t>
+          <t>ALLEMAGNE</t>
         </is>
       </c>
       <c r="B13">
-        <v>0.1166459111664591</v>
+        <v>0.02367264401624413</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CAMEROUN</t>
+          <t>ESPAGNE</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.05316007088009451</v>
+        <v>0.01977873222253789</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDE</t>
+          <t>CONGO</t>
         </is>
       </c>
       <c r="B15">
-        <v>0.06394379614193856</v>
+        <v>0.01666193158079449</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TOGO</t>
+          <t>BENIN</t>
         </is>
       </c>
       <c r="B16">
-        <v>0.1005894656778855</v>
+        <v>0.01613550144559386</v>
       </c>
     </row>
   </sheetData>
@@ -697,6 +698,178 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nationalite</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>part_occitanie</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MAROC</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>0.09366939553661545</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ALGERIE</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0.07902439024390244</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CHINE</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0.07254555636927584</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SENEGAL</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0.09554535302146669</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TUNISIE</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0.1058588036030487</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ESPAGNE</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0.1464467396331124</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LIBAN</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0.09932375316990702</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ITALIE</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0.06785101142046727</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BENIN</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0.1038307751837998</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>COTE D'IVOIRE</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.07771507771507771</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GABON</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>0.1343088010482638</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MADAGASCAR</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>0.1166459111664591</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CAMEROUN</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.05316007088009451</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INDE</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>0.06394379614193856</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TOGO</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.1005894656778855</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
